--- a/output/pdf_financials_xlsx/FFH.xlsx
+++ b/output/pdf_financials_xlsx/FFH.xlsx
@@ -27914,7 +27914,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -30048,7 +30048,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E357" s="5" t="n">

--- a/output/pdf_financials_xlsx/FFH.xlsx
+++ b/output/pdf_financials_xlsx/FFH.xlsx
@@ -5791,37 +5791,37 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>0</v>
+        <v>-0.0066</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>0</v>
+        <v>-41.2</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0</v>
+        <v>-0.0675</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>0</v>
+        <v>-0.1595</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>0</v>
+        <v>-0.1977</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>0</v>
+        <v>-0.1756</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>0</v>
+        <v>-0.261</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>0</v>
+        <v>-0.2045</v>
       </c>
       <c r="K126" s="3" t="n">
-        <v>0</v>
+        <v>-0.2947</v>
       </c>
       <c r="L126" s="3" t="n">
-        <v>0</v>
+        <v>-0.1818</v>
       </c>
     </row>
     <row r="127">
@@ -18790,7 +18790,11 @@
           <t>Dividends paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -19967,7 +19971,11 @@
           <t>Dividends paid to non-controlling interests 16</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -21143,7 +21151,11 @@
           <t>Dividends paid to non-controlling interests 16</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -24705,7 +24717,11 @@
           <t>Dividends paid to non-controlling interests 16</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -25951,7 +25967,11 @@
           <t>Dividends paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E294" s="5" t="n">
         <v>-0.0066</v>
       </c>
